--- a/DesignData/Original_Item.xlsx
+++ b/DesignData/Original_Item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\Projects\Project_MMORPG\DesignData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF27072-6E1A-48AE-83D3-6DF6D51F559F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6470A7-737C-4D5A-A7D7-2A902F928261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="전사 장비(1000~1999)" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="118">
   <si>
     <t>class_requirement</t>
   </si>
@@ -127,25 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Assets/Icon/HpPotion.HpPotion"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Assets/Icon/MpPotion.MpPotion"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Assets/Icon/MixPotion.MixPotion"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Assets/Icon/Sword_6.Sword_6"</t>
-  </si>
-  <si>
     <t>"왕가의 숨겨진 유물 중 하나. 악마와 계약해 얻은 검이라는 소문이 돈다."</t>
   </si>
   <si>
@@ -165,9 +146,6 @@
     <t>"저주받은 파멸의 검"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_6.Boots_6"</t>
-  </si>
-  <si>
     <t>"압도적인 무게감을 가진 신발. 보기만해도 두려워진다."</t>
   </si>
   <si>
@@ -180,9 +158,6 @@
     <t>"기사 단장의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_6.Gloves_6"</t>
-  </si>
-  <si>
     <t>"압도적인 무게감을 가진 건틀릿. 보기만해도 두려워진다."</t>
   </si>
   <si>
@@ -192,9 +167,6 @@
     <t>"기사 단장의 건틀릿"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_6.Legs_6"</t>
-  </si>
-  <si>
     <t>"압도적인 무게감을 가진 하의. 보기만해도 두려워진다."</t>
   </si>
   <si>
@@ -204,9 +176,6 @@
     <t>"기사 단장의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_6.Chest_6"</t>
-  </si>
-  <si>
     <t>"압도적인 무게감을 가진 상의. 보기만해도 두려워진다."</t>
   </si>
   <si>
@@ -216,9 +185,6 @@
     <t>"기사 단장의 상의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Helmet_6.Helmet_6"</t>
-  </si>
-  <si>
     <t>"압도적인 무게감을 가진 투구. 보기만해도 두려워진다."</t>
   </si>
   <si>
@@ -228,271 +194,175 @@
     <t>"기사 단장의 투구"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Sword_5.Sword_5"</t>
-  </si>
-  <si>
     <t>"글라디우스"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_5.Boots_5"</t>
-  </si>
-  <si>
     <t>"왕실 기사단에 입단할때 수여받는 신발. 품질이 우수한걸로 유명하다."</t>
   </si>
   <si>
     <t>"왕실 기사단의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_5.Gloves_5"</t>
-  </si>
-  <si>
     <t>"왕실 기사단에 입단할때 수여받는 건틀릿. 품질이 우수한걸로 유명하다."</t>
   </si>
   <si>
     <t>"왕실 기사단의 건틀릿"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_5.Legs_5"</t>
-  </si>
-  <si>
     <t>"왕실 기사단에 입단할때 수여받는 하의. 품질이 우수한걸로 유명하다."</t>
   </si>
   <si>
     <t>"왕실 기사단의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_5.Chest_5"</t>
-  </si>
-  <si>
     <t>"왕실 기사단에 입단할때 수여받는 상의. 품질이 우수한걸로 유명하다."</t>
   </si>
   <si>
     <t>"왕실 기사단의 상의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Helmet_5.Helmet_5"</t>
-  </si>
-  <si>
     <t>"왕실 기사단에 입단할때 수여받는 투구. 품질이 우수한걸로 유명하다."</t>
   </si>
   <si>
     <t>"왕실 기사단의 투구"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Sword_4.Sword_4"</t>
-  </si>
-  <si>
     <t>"전설로 내려오는 엑스칼리버를 본떠 만든 모조품. 선봉대들 사이에서 인기이다."</t>
   </si>
   <si>
     <t>"엑스칼리버(모조품)"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_4.Boots_4"</t>
-  </si>
-  <si>
     <t>"선봉대의 신발. 실력있는 기사만이 입을 수 있다."</t>
   </si>
   <si>
     <t>"선봉대의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_4.Gloves_4"</t>
-  </si>
-  <si>
     <t>"선봉대의 건틀릿. 실력있는 기사만이 입을 수 있다."</t>
   </si>
   <si>
     <t>"선봉대의 건틀릿"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_4.Legs_4"</t>
-  </si>
-  <si>
     <t>"선봉대의 하의. 실력있는 기사만이 입을 수 있다."</t>
   </si>
   <si>
     <t>"선봉대의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_4.Chest_4"</t>
-  </si>
-  <si>
     <t>"선봉대의 상의. 실력있는 기사만이 입을 수 있다."</t>
   </si>
   <si>
     <t>"선봉대의 상의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Helmet_4.Helmet_4"</t>
-  </si>
-  <si>
     <t>"선봉대의 투구. 실력있는 기사만이 입을 수 있다."</t>
   </si>
   <si>
     <t>"선봉대의 투구"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Sword_3.Sword_3"</t>
-  </si>
-  <si>
     <t>"견습 기사의 A급 검. 사용감이 적어서 그런지 날이 날렵하다."</t>
   </si>
   <si>
     <t>"기사의 검"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_3.Boots_3"</t>
-  </si>
-  <si>
     <t>"간단한 디자인의 신발. 판금으로 제작되어 꽤 단단하다."</t>
   </si>
   <si>
     <t>"견습 기사의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_3.Gloves_3"</t>
-  </si>
-  <si>
     <t>"간단한 디자인의 건틀릿. 판금으로 제작되어 꽤 단단하다."</t>
   </si>
   <si>
     <t>"견습 기사의 건틀릿"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_3.Legs_3"</t>
-  </si>
-  <si>
     <t>"간단한 디자인의 하의. 판금으로 제작되어 꽤 단단하다."</t>
   </si>
   <si>
     <t>"견습 기사의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_3.Chest_3"</t>
-  </si>
-  <si>
     <t>"간단한 디자인의 상의. 판금으로 제작되어 꽤 단단하다."</t>
   </si>
   <si>
     <t>"견습 기사의 상의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Helmet_3.Helmet_3"</t>
-  </si>
-  <si>
     <t>"간단한 디자인의 투구. 판금으로 제작되어 꽤 단단하다."</t>
   </si>
   <si>
     <t>"견습 기사의 투구"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Sword_2.Sword_2"</t>
-  </si>
-  <si>
     <t>"검은날이 매력적인 검. 밤에 휘두르면 잘 보이지 않는다."</t>
   </si>
   <si>
     <t>"흑기사의 검"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_2.Boots_2"</t>
-  </si>
-  <si>
     <t>"흑기사가 임무를 수행할때 착용하는 신발. 암살용이라 방어력은 그닥 높지 않다."</t>
   </si>
   <si>
     <t>"흑기사의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_2.Gloves_2"</t>
-  </si>
-  <si>
     <t>"흑기사가 임무를 수행할때 착용하는 건틀릿. 암살용이라 방어력은 그닥 높지 않다."</t>
   </si>
   <si>
     <t>"흑기사의 건틀릿"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_2.Legs_2"</t>
-  </si>
-  <si>
     <t>"흑기사가 임무를 수행할때 착용하는 하의. 암살용이라 방어력은 그닥 높지 않다."</t>
   </si>
   <si>
     <t>"흑기사의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_2.Chest_2"</t>
-  </si>
-  <si>
     <t>"흑기사가 임무를 수행할때 착용하는 상의. 암살용이라 방어력은 그닥 높지 않다."</t>
   </si>
   <si>
     <t>"흑기사의 상의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Helmet_2.Helmet_2"</t>
-  </si>
-  <si>
     <t>"흑기사가 임무를 수행할때 착용하는 복면. 암살용이라 방어력은 그닥 높지 않다."</t>
   </si>
   <si>
     <t>"흑기사의 복면"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Sword_1.Sword_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"FALSE"</t>
   </si>
   <si>
     <t>"초보자의 검"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Boots_1.Boots_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"허름한 신발. 입지 않은 것보다 나은 정도다."</t>
   </si>
   <si>
     <t>"초보자의 신발"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Gloves_1.Gloves_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"허름한 장갑. 입지 않은 것보다 나은 정도다."</t>
   </si>
   <si>
     <t>"초보자의 장갑"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Legs_1.Legs_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"허름한 하의. 입지 않은 것보다 나은 정도다."</t>
   </si>
   <si>
     <t>"초보자의 하의"</t>
   </si>
   <si>
-    <t>"/Game/Assets/Icon/Chest_1.Chest_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"허름한 상의. 입지 않은 것보다 나은 정도다."</t>
   </si>
   <si>
     <t>"초보자의 상의"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Icon/Helmet_1.Helmet_1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"허름한 두건. 입지 않은 것보다 나은 정도다."</t>
@@ -542,122 +412,6 @@
   </si>
   <si>
     <t>"금으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Helmet.SK_Level0_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Chest.SK_Level0_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Legs.SK_Level0_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Arms.SK_Level0_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Boots.SK_Level0_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level0_Sword.SM_Level0_Sword"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Helmet.SK_Level10_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Chest.SK_Level10_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Legs.SK_Level10_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Arms.SK_Level10_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Boots.SK_Level10_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level10_Sword.SM_Level10_Sword"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Helmet.SK_Level20_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Chest.SK_Level20_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Legs.SK_Level20_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Arms.SK_Level20_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Boots.SK_Level20_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level20_Sword.SM_Level20_Sword"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Helmet.SK_Level30_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Chest.SK_Level30_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Legs.SK_Level30_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Arms.SK_Level30_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Boots.SK_Level30_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level30_Sword.SM_Level30_Sword"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Helmet.SK_Level40_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Chest.SK_Level40_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Legs.SK_Level40_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Arms.SK_Level40_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Boots.SK_Level40_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level40_Sword.SM_Level40_Sword"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Helmet.SK_Level50_Helmet"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Chest.SK_Level50_Chest"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Legs.SK_Level50_Legs"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Arms.SK_Level50_Arms"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Boots.SK_Level50_Boots"</t>
-  </si>
-  <si>
-    <t>"/Game/Assets/Swords/SM_Level50_Sword.SM_Level50_Sword"</t>
-  </si>
-  <si>
-    <t>skeletal_mesh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>static_mesh</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1022,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E21C8A9-CEC2-4794-9B99-BAC1321823BA}">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
@@ -1037,16 +791,15 @@
     <col min="11" max="11" width="9.59765625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1075,7 +828,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1087,34 +840,25 @@
         <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="O1" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="P1" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="Q1" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="R1" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="S1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" t="s">
-        <v>148</v>
-      </c>
-      <c r="U1" t="s">
-        <v>194</v>
-      </c>
-      <c r="V1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1155,7 +899,7 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2" t="s">
         <v>13</v>
@@ -1172,34 +916,25 @@
       <c r="S2" t="s">
         <v>13</v>
       </c>
-      <c r="T2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -1209,10 +944,10 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1221,52 +956,46 @@
         <v>-1</v>
       </c>
       <c r="M3" t="s">
-        <v>145</v>
-      </c>
-      <c r="N3" t="s">
-        <v>144</v>
+        <v>105</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q3">
-        <v>100</v>
+        <f t="shared" ref="Q3:Q38" si="1">P3*0.5</f>
+        <v>50</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R38" si="1">Q3*0.5</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -1276,10 +1005,10 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1288,52 +1017,46 @@
         <v>-1</v>
       </c>
       <c r="M4" t="s">
-        <v>142</v>
-      </c>
-      <c r="N4" t="s">
-        <v>141</v>
+        <v>103</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q4">
-        <v>200</v>
-      </c>
-      <c r="R4">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -1343,10 +1066,10 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1355,52 +1078,46 @@
         <v>-1</v>
       </c>
       <c r="M5" t="s">
-        <v>139</v>
-      </c>
-      <c r="N5" t="s">
-        <v>138</v>
+        <v>101</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q5">
-        <v>200</v>
-      </c>
-      <c r="R5">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -1410,10 +1127,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J6" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1422,52 +1139,46 @@
         <v>-1</v>
       </c>
       <c r="M6" t="s">
-        <v>136</v>
-      </c>
-      <c r="N6" t="s">
-        <v>135</v>
+        <v>99</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -1477,10 +1188,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1489,52 +1200,46 @@
         <v>-1</v>
       </c>
       <c r="M7" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" t="s">
-        <v>132</v>
+        <v>97</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -1543,10 +1248,10 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="J8" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1555,52 +1260,46 @@
         <v>-1</v>
       </c>
       <c r="M8" t="s">
-        <v>156</v>
-      </c>
-      <c r="N8" t="s">
-        <v>129</v>
+        <v>116</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G9">
         <v>1000</v>
@@ -1610,10 +1309,10 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1622,52 +1321,46 @@
         <v>-1</v>
       </c>
       <c r="M9" t="s">
-        <v>127</v>
-      </c>
-      <c r="N9" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q9">
-        <v>200</v>
-      </c>
-      <c r="R9">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G10">
         <v>1000</v>
@@ -1677,10 +1370,10 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1689,52 +1382,46 @@
         <v>-1</v>
       </c>
       <c r="M10" t="s">
-        <v>124</v>
-      </c>
-      <c r="N10" t="s">
-        <v>123</v>
+        <v>91</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q10">
-        <v>400</v>
-      </c>
-      <c r="R10">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
         <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G11">
         <v>1000</v>
@@ -1744,10 +1431,10 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J11" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1756,52 +1443,46 @@
         <v>-1</v>
       </c>
       <c r="M11" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11" t="s">
-        <v>120</v>
+        <v>89</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q11">
-        <v>400</v>
-      </c>
-      <c r="R11">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G12">
         <v>1000</v>
@@ -1811,10 +1492,10 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J12" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1823,52 +1504,46 @@
         <v>-1</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N12" t="s">
-        <v>117</v>
+        <v>87</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q12">
-        <v>200</v>
-      </c>
-      <c r="R12">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <v>1000</v>
@@ -1878,10 +1553,10 @@
         <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J13" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1890,52 +1565,46 @@
         <v>-1</v>
       </c>
       <c r="M13" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13" t="s">
-        <v>114</v>
+        <v>85</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q13">
-        <v>200</v>
-      </c>
-      <c r="R13">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1011</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>2000</v>
@@ -1945,10 +1614,10 @@
         <v>200</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1957,52 +1626,46 @@
         <v>-1</v>
       </c>
       <c r="M14" t="s">
-        <v>112</v>
-      </c>
-      <c r="N14" t="s">
-        <v>111</v>
+        <v>83</v>
+      </c>
+      <c r="N14">
+        <v>35</v>
       </c>
       <c r="O14">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1012</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E15">
         <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G15">
         <v>3000</v>
@@ -2012,10 +1675,10 @@
         <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J15" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2024,52 +1687,46 @@
         <v>-1</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
-      </c>
-      <c r="N15" t="s">
-        <v>108</v>
+        <v>81</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q15">
-        <v>400</v>
-      </c>
-      <c r="R15">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G16">
         <v>3000</v>
@@ -2079,10 +1736,10 @@
         <v>300</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J16" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2091,52 +1748,46 @@
         <v>-1</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
-      </c>
-      <c r="N16" t="s">
-        <v>105</v>
+        <v>79</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q16">
-        <v>800</v>
-      </c>
-      <c r="R16">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
         <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
       </c>
       <c r="E17">
         <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G17">
         <v>3000</v>
@@ -2146,10 +1797,10 @@
         <v>300</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J17" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2158,52 +1809,46 @@
         <v>-1</v>
       </c>
       <c r="M17" t="s">
-        <v>103</v>
-      </c>
-      <c r="N17" t="s">
-        <v>102</v>
+        <v>77</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q17">
-        <v>800</v>
-      </c>
-      <c r="R17">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1015</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G18">
         <v>3000</v>
@@ -2213,10 +1858,10 @@
         <v>300</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J18" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2225,52 +1870,46 @@
         <v>-1</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N18" t="s">
-        <v>99</v>
+        <v>75</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q18">
-        <v>400</v>
-      </c>
-      <c r="R18">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1016</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G19">
         <v>3000</v>
@@ -2280,10 +1919,10 @@
         <v>300</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J19" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2292,52 +1931,46 @@
         <v>-1</v>
       </c>
       <c r="M19" t="s">
-        <v>97</v>
-      </c>
-      <c r="N19" t="s">
-        <v>96</v>
+        <v>73</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q19">
-        <v>400</v>
-      </c>
-      <c r="R19">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
       <c r="S19">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E20">
         <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G20">
         <v>5000</v>
@@ -2347,10 +1980,10 @@
         <v>500</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J20" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2359,52 +1992,46 @@
         <v>-1</v>
       </c>
       <c r="M20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" t="s">
-        <v>93</v>
+        <v>71</v>
+      </c>
+      <c r="N20">
+        <v>80</v>
       </c>
       <c r="O20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R20">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1018</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E21">
         <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G21">
         <v>8000</v>
@@ -2414,10 +2041,10 @@
         <v>800</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J21" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2426,52 +2053,46 @@
         <v>-1</v>
       </c>
       <c r="M21" t="s">
-        <v>91</v>
-      </c>
-      <c r="N21" t="s">
-        <v>90</v>
+        <v>69</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q21">
-        <v>800</v>
-      </c>
-      <c r="R21">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
       <c r="S21">
         <v>0</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1019</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E22">
         <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G22">
         <v>8000</v>
@@ -2481,10 +2102,10 @@
         <v>800</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J22" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2493,52 +2114,46 @@
         <v>-1</v>
       </c>
       <c r="M22" t="s">
-        <v>88</v>
-      </c>
-      <c r="N22" t="s">
-        <v>87</v>
+        <v>67</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q22">
-        <v>1600</v>
-      </c>
-      <c r="R22">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1020</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
         <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
       </c>
       <c r="E23">
         <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G23">
         <v>8000</v>
@@ -2548,10 +2163,10 @@
         <v>800</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J23" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2560,52 +2175,46 @@
         <v>-1</v>
       </c>
       <c r="M23" t="s">
-        <v>85</v>
-      </c>
-      <c r="N23" t="s">
-        <v>84</v>
+        <v>65</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q23">
-        <v>1600</v>
-      </c>
-      <c r="R23">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G24">
         <v>8000</v>
@@ -2615,10 +2224,10 @@
         <v>800</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2627,52 +2236,46 @@
         <v>-1</v>
       </c>
       <c r="M24" t="s">
-        <v>82</v>
-      </c>
-      <c r="N24" t="s">
-        <v>81</v>
+        <v>63</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q24">
-        <v>800</v>
-      </c>
-      <c r="R24">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1022</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E25">
         <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G25">
         <v>8000</v>
@@ -2682,10 +2285,10 @@
         <v>800</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J25" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2694,52 +2297,46 @@
         <v>-1</v>
       </c>
       <c r="M25" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q25">
-        <v>800</v>
-      </c>
-      <c r="R25">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1023</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E26">
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G26">
         <v>15000</v>
@@ -2749,10 +2346,10 @@
         <v>1500</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2761,52 +2358,46 @@
         <v>-1</v>
       </c>
       <c r="M26" t="s">
-        <v>76</v>
-      </c>
-      <c r="N26" t="s">
-        <v>75</v>
+        <v>59</v>
+      </c>
+      <c r="N26">
+        <v>120</v>
       </c>
       <c r="O26">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R26">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="V26" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E27">
         <v>40</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G27">
         <v>12000</v>
@@ -2816,10 +2407,10 @@
         <v>1200</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J27" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2828,52 +2419,46 @@
         <v>-1</v>
       </c>
       <c r="M27" t="s">
-        <v>73</v>
-      </c>
-      <c r="N27" t="s">
-        <v>72</v>
+        <v>57</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q27">
-        <v>1600</v>
-      </c>
-      <c r="R27">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
       <c r="S27">
         <v>0</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>40</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G28">
         <v>12000</v>
@@ -2883,10 +2468,10 @@
         <v>1200</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J28" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2895,52 +2480,46 @@
         <v>-1</v>
       </c>
       <c r="M28" t="s">
-        <v>70</v>
-      </c>
-      <c r="N28" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="Q28">
-        <v>3200</v>
-      </c>
-      <c r="R28">
         <f t="shared" si="1"/>
         <v>1600</v>
       </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1026</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
         <v>40</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
       </c>
       <c r="E29">
         <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G29">
         <v>12000</v>
@@ -2950,10 +2529,10 @@
         <v>1200</v>
       </c>
       <c r="I29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2962,52 +2541,46 @@
         <v>-1</v>
       </c>
       <c r="M29" t="s">
-        <v>67</v>
-      </c>
-      <c r="N29" t="s">
-        <v>66</v>
+        <v>53</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="Q29">
-        <v>3200</v>
-      </c>
-      <c r="R29">
         <f t="shared" si="1"/>
         <v>1600</v>
       </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1027</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G30">
         <v>12000</v>
@@ -3017,10 +2590,10 @@
         <v>1200</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -3029,52 +2602,46 @@
         <v>-1</v>
       </c>
       <c r="M30" t="s">
-        <v>64</v>
-      </c>
-      <c r="N30" t="s">
-        <v>63</v>
+        <v>51</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q30">
-        <v>1600</v>
-      </c>
-      <c r="R30">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
       <c r="S30">
         <v>0</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>1028</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E31">
         <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G31">
         <v>12000</v>
@@ -3084,10 +2651,10 @@
         <v>1200</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J31" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3096,52 +2663,46 @@
         <v>-1</v>
       </c>
       <c r="M31" t="s">
-        <v>61</v>
-      </c>
-      <c r="N31" t="s">
-        <v>60</v>
+        <v>49</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="Q31">
-        <v>1600</v>
-      </c>
-      <c r="R31">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
       <c r="S31">
         <v>0</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>1029</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E32">
         <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G32">
         <v>20000</v>
@@ -3151,10 +2712,10 @@
         <v>2000</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -3163,52 +2724,46 @@
         <v>-1</v>
       </c>
       <c r="M32" t="s">
-        <v>157</v>
-      </c>
-      <c r="N32" t="s">
-        <v>58</v>
+        <v>117</v>
+      </c>
+      <c r="N32">
+        <v>180</v>
       </c>
       <c r="O32">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R32">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="V32" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>1030</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G33">
         <v>35000</v>
@@ -3218,10 +2773,10 @@
         <v>3500</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3230,52 +2785,46 @@
         <v>-1</v>
       </c>
       <c r="M33" t="s">
-        <v>55</v>
-      </c>
-      <c r="N33" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Q33">
-        <v>4000</v>
-      </c>
-      <c r="R33">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
       <c r="S33">
         <v>0</v>
       </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>1031</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G34">
         <v>35000</v>
@@ -3285,10 +2834,10 @@
         <v>3500</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3297,52 +2846,46 @@
         <v>-1</v>
       </c>
       <c r="M34" t="s">
-        <v>51</v>
-      </c>
-      <c r="N34" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Q34">
-        <v>8000</v>
-      </c>
-      <c r="R34">
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1032</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
         <v>40</v>
-      </c>
-      <c r="D35" t="s">
-        <v>48</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G35">
         <v>35000</v>
@@ -3352,10 +2895,10 @@
         <v>3500</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -3364,52 +2907,46 @@
         <v>-1</v>
       </c>
       <c r="M35" t="s">
-        <v>47</v>
-      </c>
-      <c r="N35" t="s">
-        <v>46</v>
+        <v>39</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Q35">
-        <v>8000</v>
-      </c>
-      <c r="R35">
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
       <c r="S35">
         <v>0</v>
       </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1033</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G36">
         <v>35000</v>
@@ -3419,10 +2956,10 @@
         <v>3500</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J36" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3431,52 +2968,46 @@
         <v>-1</v>
       </c>
       <c r="M36" t="s">
-        <v>43</v>
-      </c>
-      <c r="N36" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Q36">
-        <v>4000</v>
-      </c>
-      <c r="R36">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
       <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1034</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E37">
         <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G37">
         <v>35000</v>
@@ -3486,64 +3017,58 @@
         <v>3500</v>
       </c>
       <c r="I37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>-1</v>
+      </c>
+      <c r="M37" t="s">
         <v>32</v>
       </c>
-      <c r="J37" t="s">
-        <v>155</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37">
-        <v>-1</v>
-      </c>
-      <c r="M37" t="s">
-        <v>38</v>
-      </c>
-      <c r="N37" t="s">
-        <v>37</v>
+      <c r="N37">
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Q37">
-        <v>4000</v>
-      </c>
-      <c r="R37">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
       <c r="S37">
         <v>0</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1035</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E38">
         <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G38">
         <v>80000</v>
@@ -3553,10 +3078,10 @@
         <v>8000</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J38" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3565,32 +3090,26 @@
         <v>-1</v>
       </c>
       <c r="M38" t="s">
-        <v>31</v>
-      </c>
-      <c r="N38" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="N38">
+        <v>300</v>
       </c>
       <c r="O38">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R38">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="V38" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3602,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C008D5-5B4B-40C3-9807-A1000646DEFB}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
@@ -3615,12 +3134,11 @@
     <col min="9" max="9" width="7.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="39.09765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3649,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3661,16 +3179,13 @@
         <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3711,16 +3226,13 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -3761,17 +3273,14 @@
       <c r="M3" t="s">
         <v>23</v>
       </c>
-      <c r="N3" t="s">
-        <v>27</v>
+      <c r="N3">
+        <v>0.3</v>
       </c>
       <c r="O3">
-        <v>0.3</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -3812,17 +3321,14 @@
       <c r="M4" t="s">
         <v>22</v>
       </c>
-      <c r="N4" t="s">
-        <v>28</v>
+      <c r="N4">
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -3863,13 +3369,10 @@
       <c r="M5" t="s">
         <v>24</v>
       </c>
-      <c r="N5" t="s">
-        <v>29</v>
+      <c r="N5">
+        <v>0.4</v>
       </c>
       <c r="O5">
-        <v>0.4</v>
-      </c>
-      <c r="P5">
         <v>0.4</v>
       </c>
     </row>
@@ -3881,13 +3384,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="23" max="23" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3916,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3928,16 +3431,13 @@
         <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3978,12 +3478,9 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" t="s">
         <v>13</v>
       </c>
     </row>

--- a/DesignData/Original_Item.xlsx
+++ b/DesignData/Original_Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\Projects\Project_MMORPG\DesignData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6470A7-737C-4D5A-A7D7-2A902F928261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BAB660-6A70-4EC6-9179-04E4AE372809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="전사 장비(1000~1999)" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="117">
   <si>
     <t>class_requirement</t>
   </si>
@@ -99,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"consumption"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"all"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,9 +136,6 @@
     <t>"sword"</t>
   </si>
   <si>
-    <t>"weapon"</t>
-  </si>
-  <si>
     <t>"저주받은 파멸의 검"</t>
   </si>
   <si>
@@ -150,9 +143,6 @@
   </si>
   <si>
     <t>"boots"</t>
-  </si>
-  <si>
-    <t>"armor"</t>
   </si>
   <si>
     <t>"기사 단장의 신발"</t>
@@ -413,6 +403,12 @@
   <si>
     <t>"금으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"GEAR"</t>
+  </si>
+  <si>
+    <t>"CONSUMABLE"</t>
   </si>
 </sst>
 </file>
@@ -801,7 +797,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -828,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -840,22 +836,22 @@
         <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="R1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="S1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
@@ -922,19 +918,19 @@
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -944,10 +940,10 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -956,7 +952,7 @@
         <v>-1</v>
       </c>
       <c r="M3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -983,19 +979,19 @@
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -1005,10 +1001,10 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1017,7 +1013,7 @@
         <v>-1</v>
       </c>
       <c r="M4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1044,19 +1040,19 @@
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -1066,10 +1062,10 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1078,7 +1074,7 @@
         <v>-1</v>
       </c>
       <c r="M5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1105,19 +1101,19 @@
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -1127,10 +1123,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1139,7 +1135,7 @@
         <v>-1</v>
       </c>
       <c r="M6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1166,19 +1162,19 @@
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -1188,10 +1184,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1200,7 +1196,7 @@
         <v>-1</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1227,19 +1223,19 @@
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -1248,10 +1244,10 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1260,7 +1256,7 @@
         <v>-1</v>
       </c>
       <c r="M8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -1287,19 +1283,19 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>1000</v>
@@ -1309,10 +1305,10 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1321,7 +1317,7 @@
         <v>-1</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1348,19 +1344,19 @@
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>1000</v>
@@ -1370,10 +1366,10 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1382,7 +1378,7 @@
         <v>-1</v>
       </c>
       <c r="M10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1409,19 +1405,19 @@
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11">
         <v>1000</v>
@@ -1431,10 +1427,10 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1443,7 +1439,7 @@
         <v>-1</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1470,19 +1466,19 @@
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" t="s">
         <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
       </c>
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12">
         <v>1000</v>
@@ -1492,10 +1488,10 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1504,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1531,19 +1527,19 @@
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13">
         <v>1000</v>
@@ -1553,10 +1549,10 @@
         <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1565,7 +1561,7 @@
         <v>-1</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1592,19 +1588,19 @@
         <v>1011</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14">
         <v>2000</v>
@@ -1614,10 +1610,10 @@
         <v>200</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1626,7 +1622,7 @@
         <v>-1</v>
       </c>
       <c r="M14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N14">
         <v>35</v>
@@ -1653,19 +1649,19 @@
         <v>1012</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15">
         <v>3000</v>
@@ -1675,10 +1671,10 @@
         <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1687,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1714,19 +1710,19 @@
         <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E16">
         <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16">
         <v>3000</v>
@@ -1736,10 +1732,10 @@
         <v>300</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1748,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1775,19 +1771,19 @@
         <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17">
         <v>3000</v>
@@ -1797,10 +1793,10 @@
         <v>300</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1809,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="M17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1836,19 +1832,19 @@
         <v>1015</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" t="s">
         <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
       </c>
       <c r="E18">
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18">
         <v>3000</v>
@@ -1858,10 +1854,10 @@
         <v>300</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1870,7 +1866,7 @@
         <v>-1</v>
       </c>
       <c r="M18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1897,19 +1893,19 @@
         <v>1016</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19">
         <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19">
         <v>3000</v>
@@ -1919,10 +1915,10 @@
         <v>300</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1931,7 +1927,7 @@
         <v>-1</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -1958,19 +1954,19 @@
         <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20">
         <v>5000</v>
@@ -1980,10 +1976,10 @@
         <v>500</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -1992,7 +1988,7 @@
         <v>-1</v>
       </c>
       <c r="M20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N20">
         <v>80</v>
@@ -2019,19 +2015,19 @@
         <v>1018</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21">
         <v>8000</v>
@@ -2041,10 +2037,10 @@
         <v>800</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2053,7 +2049,7 @@
         <v>-1</v>
       </c>
       <c r="M21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2080,19 +2076,19 @@
         <v>1019</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E22">
         <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22">
         <v>8000</v>
@@ -2102,10 +2098,10 @@
         <v>800</v>
       </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2114,7 +2110,7 @@
         <v>-1</v>
       </c>
       <c r="M22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2141,19 +2137,19 @@
         <v>1020</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23">
         <v>8000</v>
@@ -2163,10 +2159,10 @@
         <v>800</v>
       </c>
       <c r="I23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2175,7 +2171,7 @@
         <v>-1</v>
       </c>
       <c r="M23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2202,19 +2198,19 @@
         <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" t="s">
         <v>34</v>
-      </c>
-      <c r="D24" t="s">
-        <v>37</v>
       </c>
       <c r="E24">
         <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24">
         <v>8000</v>
@@ -2224,10 +2220,10 @@
         <v>800</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2236,7 +2232,7 @@
         <v>-1</v>
       </c>
       <c r="M24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2263,19 +2259,19 @@
         <v>1022</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25">
         <v>8000</v>
@@ -2285,10 +2281,10 @@
         <v>800</v>
       </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2297,7 +2293,7 @@
         <v>-1</v>
       </c>
       <c r="M25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -2324,19 +2320,19 @@
         <v>1023</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26">
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26">
         <v>15000</v>
@@ -2346,10 +2342,10 @@
         <v>1500</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2358,7 +2354,7 @@
         <v>-1</v>
       </c>
       <c r="M26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N26">
         <v>120</v>
@@ -2385,19 +2381,19 @@
         <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>40</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27">
         <v>12000</v>
@@ -2407,10 +2403,10 @@
         <v>1200</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2419,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="M27" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -2446,19 +2442,19 @@
         <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>40</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28">
         <v>12000</v>
@@ -2468,10 +2464,10 @@
         <v>1200</v>
       </c>
       <c r="I28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2480,7 +2476,7 @@
         <v>-1</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -2507,19 +2503,19 @@
         <v>1026</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E29">
         <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29">
         <v>12000</v>
@@ -2529,10 +2525,10 @@
         <v>1200</v>
       </c>
       <c r="I29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2541,7 +2537,7 @@
         <v>-1</v>
       </c>
       <c r="M29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2568,19 +2564,19 @@
         <v>1027</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
         <v>34</v>
-      </c>
-      <c r="D30" t="s">
-        <v>37</v>
       </c>
       <c r="E30">
         <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30">
         <v>12000</v>
@@ -2590,10 +2586,10 @@
         <v>1200</v>
       </c>
       <c r="I30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2602,7 +2598,7 @@
         <v>-1</v>
       </c>
       <c r="M30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2629,19 +2625,19 @@
         <v>1028</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31">
         <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31">
         <v>12000</v>
@@ -2651,10 +2647,10 @@
         <v>1200</v>
       </c>
       <c r="I31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2663,7 +2659,7 @@
         <v>-1</v>
       </c>
       <c r="M31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -2690,19 +2686,19 @@
         <v>1029</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32">
         <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32">
         <v>20000</v>
@@ -2712,10 +2708,10 @@
         <v>2000</v>
       </c>
       <c r="I32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2724,7 +2720,7 @@
         <v>-1</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N32">
         <v>180</v>
@@ -2751,19 +2747,19 @@
         <v>1030</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33">
         <v>35000</v>
@@ -2773,10 +2769,10 @@
         <v>3500</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2785,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="M33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2812,19 +2808,19 @@
         <v>1031</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34">
         <v>35000</v>
@@ -2834,10 +2830,10 @@
         <v>3500</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2846,7 +2842,7 @@
         <v>-1</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -2873,19 +2869,19 @@
         <v>1032</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35">
         <v>35000</v>
@@ -2895,10 +2891,10 @@
         <v>3500</v>
       </c>
       <c r="I35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2907,7 +2903,7 @@
         <v>-1</v>
       </c>
       <c r="M35" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -2934,19 +2930,19 @@
         <v>1033</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" t="s">
         <v>34</v>
-      </c>
-      <c r="D36" t="s">
-        <v>37</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G36">
         <v>35000</v>
@@ -2956,10 +2952,10 @@
         <v>3500</v>
       </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2968,7 +2964,7 @@
         <v>-1</v>
       </c>
       <c r="M36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -2995,19 +2991,19 @@
         <v>1034</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E37">
         <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37">
         <v>35000</v>
@@ -3017,10 +3013,10 @@
         <v>3500</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3029,7 +3025,7 @@
         <v>-1</v>
       </c>
       <c r="M37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -3056,19 +3052,19 @@
         <v>1035</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38">
         <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38">
         <v>80000</v>
@@ -3078,10 +3074,10 @@
         <v>8000</v>
       </c>
       <c r="I38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3090,7 +3086,7 @@
         <v>-1</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N38">
         <v>300</v>
@@ -3126,7 +3122,7 @@
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
@@ -3140,7 +3136,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -3167,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3240,7 +3236,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -3249,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>150</v>
@@ -3259,10 +3255,10 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -3271,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>0.3</v>
@@ -3288,7 +3284,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -3297,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>150</v>
@@ -3307,10 +3303,10 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -3319,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3336,7 +3332,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -3345,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5">
         <v>250</v>
@@ -3355,10 +3351,10 @@
         <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3367,7 +3363,7 @@
         <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N5">
         <v>0.4</v>
@@ -3392,7 +3388,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -3419,7 +3415,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
